--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486890_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486890_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0375</v>
+        <v>5.2685</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9799</v>
+        <v>5.1891</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0576</v>
+        <v>0.0794</v>
       </c>
       <c r="G2" t="n">
         <v>5.0981</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8902</v>
+        <v>0.1212</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4729</v>
+        <v>-0.2637</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3631</v>
+        <v>0.3849</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5668</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2203</v>
+        <v>2.6066</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1862</v>
+        <v>4.454</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.966</v>
+        <v>-1.8474</v>
       </c>
       <c r="G3" t="n">
         <v>-1.4302</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7996</v>
+        <v>0.1859</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0613</v>
+        <v>0.3291</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2617</v>
+        <v>-0.1431</v>
       </c>
       <c r="V3" t="n">
         <v>2.8242</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.214</v>
+        <v>1.705</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7407</v>
+        <v>1.1131</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4734</v>
+        <v>0.5919</v>
       </c>
       <c r="G4" t="n">
         <v>1.089</v>
@@ -766,13 +766,13 @@
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9895</v>
+        <v>0.4804</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2784</v>
+        <v>0.6508</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2889</v>
+        <v>-0.1704</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4805</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3337</v>
+        <v>0.6929</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.161</v>
+        <v>0.2574</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4947</v>
+        <v>0.4355</v>
       </c>
       <c r="G5" t="n">
         <v>1.1811</v>
@@ -844,13 +844,13 @@
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6865</v>
+        <v>-0.3273</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4457</v>
+        <v>-0.0272</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2408</v>
+        <v>-0.3001</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1876</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2047</v>
+        <v>-0.2612</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5019</v>
+        <v>0.2769</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2972</v>
+        <v>-0.538</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7349</v>
+        <v>-0.2293</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2747</v>
+        <v>0.347</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4602</v>
+        <v>-0.5763</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6304999999999999</v>
+        <v>0.5195</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7489</v>
+        <v>0.7042</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1184</v>
+        <v>-0.1847</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1044</v>
+        <v>-0.7488</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5258</v>
+        <v>-0.3572</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5786</v>
+        <v>-0.3916</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.4374</v>
+        <v>-2.6694</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5479000000000001</v>
+        <v>-0.123</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0931</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.641</v>
+        <v>-0.1925</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1876</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6591</v>
+        <v>2.3573</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4715</v>
+        <v>-1.6501</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.574</v>
+        <v>-0.5304</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5304</v>
+        <v>0.4258</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1043</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-1.564</v>
@@ -1000,13 +1000,13 @@
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1492</v>
+        <v>-0.1056</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0854</v>
+        <v>-0.19</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0638</v>
+        <v>0.0844</v>
       </c>
       <c r="V7" t="n">
         <v>0.9339</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.424</v>
+        <v>-0.5918</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5599</v>
+        <v>-0.7111</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8641</v>
+        <v>0.1194</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2293</v>
+        <v>-1.7349</v>
       </c>
       <c r="H8" t="n">
-        <v>0.347</v>
+        <v>-1.2747</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5763</v>
+        <v>-0.4602</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5195</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7042</v>
+        <v>-0.7489</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1847</v>
+        <v>0.1184</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7488</v>
+        <v>-1.1044</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3572</v>
+        <v>-0.5258</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3916</v>
+        <v>-0.5786</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.6694</v>
+        <v>-1.4374</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2859</v>
+        <v>0.1608</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7673</v>
+        <v>-0.3023</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5185999999999999</v>
+        <v>0.4631</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7072000000000001</v>
+        <v>1.1876</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3573</v>
+        <v>1.6591</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6501</v>
+        <v>-0.4715</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1603</v>
+        <v>-2.6843</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7892</v>
+        <v>-1.58</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3711</v>
+        <v>-1.1043</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3226</v>
@@ -1156,13 +1156,13 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8993</v>
+        <v>-0.4233</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6587</v>
+        <v>-0.4495</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2406</v>
+        <v>0.0262</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3491</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4007</v>
+        <v>-3.1635</v>
       </c>
       <c r="E10" t="n">
         <v>-1.8292</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5715</v>
+        <v>-1.3343</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4166</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5742</v>
+        <v>-0.3371</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0118</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5624</v>
+        <v>-0.3253</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4098</v>
@@ -1273,16 +1273,16 @@
         <v>7.596</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5541</v>
+        <v>-4.5539</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3294</v>
+        <v>-1.329400000000001</v>
       </c>
       <c r="H11" t="n">
         <v>1.103700000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.433199999999999</v>
+        <v>-2.4332</v>
       </c>
       <c r="J11" t="n">
         <v>6.924799999999999</v>
@@ -1312,13 +1312,13 @@
         <v>13.3473</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3679000000000001</v>
+        <v>-0.3679999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1951999999999998</v>
+        <v>-0.1951</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1727</v>
+        <v>-0.1728</v>
       </c>
       <c r="V11" t="n">
         <v>1.6591</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2813</v>
+        <v>5.5717</v>
       </c>
       <c r="E12" t="n">
-        <v>6.8563</v>
+        <v>6.3333</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.575</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>2.5152</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5571</v>
+        <v>0.8475</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7746</v>
+        <v>0.2516</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7825</v>
+        <v>0.5959</v>
       </c>
       <c r="V12" t="n">
         <v>2.0037</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.883</v>
+        <v>2.868</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5697</v>
+        <v>1.9882</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3132</v>
+        <v>0.8798</v>
       </c>
       <c r="G13" t="n">
         <v>0.5011</v>
@@ -1468,13 +1468,13 @@
         <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0674</v>
+        <v>-0.0823</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4302</v>
+        <v>-0.0118</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6372</v>
+        <v>-0.0706</v>
       </c>
       <c r="V13" t="n">
         <v>2.2439</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.685</v>
+        <v>2.1057</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3962</v>
+        <v>1.7686</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7112000000000001</v>
+        <v>0.3371</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4768</v>
+        <v>2.4062</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4022</v>
+        <v>1.9594</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.879</v>
+        <v>0.4468</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4115</v>
+        <v>3.1628</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8988</v>
+        <v>2.9267</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5127</v>
+        <v>0.2361</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8883</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4967</v>
+        <v>-0.9673</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3917</v>
+        <v>0.2107</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4903</v>
+        <v>-0.0639</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8595</v>
+        <v>-0.5193</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3691</v>
+        <v>0.4554</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2875</v>
+        <v>0.5848</v>
       </c>
       <c r="W14" t="n">
         <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1088</v>
+        <v>-0.5938</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.356</v>
+        <v>1.0208</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4548</v>
+        <v>1.2456</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0988</v>
+        <v>-0.2248</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4062</v>
+        <v>-0.4768</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9594</v>
+        <v>0.4022</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4468</v>
+        <v>-0.879</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1628</v>
+        <v>1.4115</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9267</v>
+        <v>0.8988</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2361</v>
+        <v>0.5127</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-1.8883</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9673</v>
+        <v>-0.4967</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2107</v>
+        <v>-1.3917</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8136</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.7088</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0195</v>
+        <v>0.1173</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5848</v>
+        <v>1.2875</v>
       </c>
       <c r="W15" t="n">
         <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5938</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1602</v>
+        <v>0.1759</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3177</v>
+        <v>-0.2131</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4779</v>
+        <v>0.389</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2536</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0804</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2558</v>
+        <v>-0.1512</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3205</v>
+        <v>0.2316</v>
       </c>
       <c r="V16" t="n">
         <v>0.3491</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7694</v>
+        <v>0.0762</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9734</v>
+        <v>-0.555</v>
       </c>
       <c r="F17" t="n">
-        <v>0.204</v>
+        <v>0.6312</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0933</v>
@@ -1780,13 +1780,13 @@
         <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0519</v>
+        <v>-0.2064</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4534</v>
+        <v>-0.035</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5985</v>
+        <v>-0.1714</v>
       </c>
       <c r="V17" t="n">
         <v>0.3491</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3856</v>
+        <v>-1.1223</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6818</v>
+        <v>1.5772</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0674</v>
+        <v>-2.6996</v>
       </c>
       <c r="G18" t="n">
         <v>0.1432</v>
@@ -1858,13 +1858,13 @@
         <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4777</v>
+        <v>0.741</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2672</v>
+        <v>0.1626</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2105</v>
+        <v>0.5784</v>
       </c>
       <c r="V18" t="n">
         <v>-3.6492</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3211</v>
+        <v>-2.1276</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9111</v>
+        <v>-1.4927</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4099</v>
+        <v>-0.6349</v>
       </c>
       <c r="G19" t="n">
         <v>0.0302</v>
@@ -1936,13 +1936,13 @@
         <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4559</v>
+        <v>-0.2625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7014</v>
+        <v>-0.283</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2455</v>
+        <v>0.0205</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4579</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4139</v>
+        <v>-2.1541</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2722</v>
+        <v>-1.063</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1416</v>
+        <v>-1.0911</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2733</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4754</v>
+        <v>0.7352</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1744</v>
+        <v>0.0348</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6499</v>
+        <v>0.7004</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1786</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.5174</v>
+        <v>-7.364</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9304</v>
+        <v>-5.035</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.587</v>
+        <v>-2.329</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1696</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3085</v>
+        <v>-0.155</v>
       </c>
       <c r="T21" t="n">
-        <v>0.12</v>
+        <v>0.0154</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4284</v>
+        <v>-0.1704</v>
       </c>
       <c r="V21" t="n">
         <v>-3.1913</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.041899999999998</v>
+        <v>-0.9496999999999991</v>
       </c>
       <c r="E22" t="n">
-        <v>4.554000000000001</v>
+        <v>4.554099999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.595800000000001</v>
+        <v>-5.5039</v>
       </c>
       <c r="G22" t="n">
         <v>1.329300000000001</v>
@@ -2170,13 +2170,13 @@
         <v>10.2672</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3678999999999999</v>
+        <v>2.4601</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1728999999999996</v>
+        <v>0.1729</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1951999999999999</v>
+        <v>2.2871</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6589</v>
